--- a/testdata/configurationUAT/configuration_environment.xlsx
+++ b/testdata/configurationUAT/configuration_environment.xlsx
@@ -11,12 +11,25 @@
     <sheet name="Sheet1" r:id="rId2" sheetId="2"/>
     <sheet name="Conn" r:id="rId3" sheetId="3"/>
   </sheets>
-  <calcPr calcId="144525"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="89" uniqueCount="65">
   <si>
     <t>This document was exported from Numbers. Each table was converted to an Excel worksheet. All other objects on each Numbers sheet were placed on separate worksheets. Please be aware that formula calculations may differ in Excel.</t>
   </si>
@@ -159,10 +172,7 @@
     <t>.</t>
   </si>
   <si>
-    <t>co.infinum.nlb.tst.playstore</t>
-  </si>
-  <si>
-    <t>co.infinum.nlb.tst.playstore:id/</t>
+    <t>si.nlb.klik.test</t>
   </si>
   <si>
     <t>C:\Users\Bozidar Tomasevic\AppData\Local\Programs\Appium\resources\app\node_modules\appium\build\lib\main.js</t>
@@ -186,34 +196,28 @@
     <t>jdbc:sqlserver://10.1.133.30;Database=iBankingRaiffeisenV4;User Id=sa;Password=Cerkasov123;integratedSecurity=false;</t>
   </si>
   <si>
-    <t>co.infinum.nlb.uat</t>
+    <t>si.nlb.klik.uat</t>
+  </si>
+  <si>
+    <t>ON</t>
+  </si>
+  <si>
+    <t>\\10.11.1.158\03. TEST Team\NLB SLO\FileShare\UAT</t>
+  </si>
+  <si>
+    <t>MYSQL</t>
+  </si>
+  <si>
+    <t>jdbc:mysql://172.20.1.100:3306/dbnlbreport?user=adm1n&amp;password=Beograd123!&amp;useSSL=false</t>
+  </si>
+  <si>
+    <t>0</t>
+  </si>
+  <si>
+    <t>UAT 06 07 2023 09:36:41</t>
   </si>
   <si>
     <t>co.infinum.nlb.uat:id/</t>
-  </si>
-  <si>
-    <t>ON</t>
-  </si>
-  <si>
-    <t>\\10.11.1.158\03. TEST Team\NLB SLO\FileShare\UAT</t>
-  </si>
-  <si>
-    <t>MYSQL</t>
-  </si>
-  <si>
-    <t>jdbc:mysql://172.20.1.100:3306/dbnlbreport?user=adm1n&amp;password=Beograd123!&amp;useSSL=false</t>
-  </si>
-  <si>
-    <t>0</t>
-  </si>
-  <si>
-    <t>UAT 06 07 2023 09:36:41</t>
-  </si>
-  <si>
-    <t>co.infinum.nlb.qa.playstore</t>
-  </si>
-  <si>
-    <t>co.infinum.nlb.qa.playstore:id/</t>
   </si>
   <si>
     <t>jdbc:sqlserver://DTC-01\SQLEXPRESS;Database=test;integratedSecurity=true</t>
@@ -243,7 +247,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
   <numFmts count="4">
     <numFmt numFmtId="42" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;_);_(@_)"/>
     <numFmt numFmtId="44" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
@@ -2569,23 +2573,23 @@
         <v>41</v>
       </c>
       <c r="L2" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="M2" s="7" t="s">
         <v>42</v>
       </c>
-      <c r="M2" s="7" t="s">
+      <c r="N2" s="9" t="s">
         <v>43</v>
       </c>
-      <c r="N2" s="9" t="s">
+      <c r="O2" s="10" t="s">
         <v>44</v>
-      </c>
-      <c r="O2" s="10" t="s">
-        <v>45</v>
       </c>
       <c r="P2" s="11"/>
       <c r="Q2" s="10" t="s">
+        <v>45</v>
+      </c>
+      <c r="R2" s="10" t="s">
         <v>46</v>
-      </c>
-      <c r="R2" s="10" t="s">
-        <v>47</v>
       </c>
     </row>
     <row customHeight="1" ht="13.5" r="3" spans="1:24">
@@ -2599,13 +2603,13 @@
         <v>34</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E3" s="3" t="s">
         <v>36</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="G3" s="3" t="s">
         <v>40</v>
@@ -2620,10 +2624,10 @@
         <v>40</v>
       </c>
       <c r="K3" s="7" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="L3" s="7" t="s">
-        <v>51</v>
+        <v>40</v>
       </c>
       <c r="M3" s="7"/>
       <c r="N3" s="7"/>
@@ -2632,22 +2636,22 @@
       <c r="Q3" s="7"/>
       <c r="R3" s="7"/>
       <c r="S3" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="T3" s="14" t="s">
+        <v>51</v>
+      </c>
+      <c r="U3" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="T3" s="14" t="s">
+      <c r="V3" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="U3" s="1" t="s">
+      <c r="W3" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="V3" s="1" t="s">
+      <c r="X3" s="1" t="s">
         <v>55</v>
-      </c>
-      <c r="W3" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="X3" s="1" t="s">
-        <v>57</v>
       </c>
     </row>
     <row customHeight="1" ht="13.5" r="4" spans="1:18">
@@ -2662,10 +2666,10 @@
       <c r="I4" s="4"/>
       <c r="J4" s="4"/>
       <c r="K4" s="7" t="s">
-        <v>58</v>
+        <v>49</v>
       </c>
       <c r="L4" s="7" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="M4" s="12"/>
       <c r="N4" s="12"/>
@@ -2841,7 +2845,7 @@
         <v>36</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="C2" s="4"/>
       <c r="D2" s="4"/>
@@ -2849,27 +2853,27 @@
     </row>
     <row customHeight="1" ht="13.5" r="3" spans="1:5">
       <c r="A3" s="3" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B3" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="E3" s="3" t="s">
         <v>61</v>
-      </c>
-      <c r="C3" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="D3" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="E3" s="3" t="s">
-        <v>64</v>
       </c>
     </row>
     <row customHeight="1" ht="13.5" r="4" spans="1:5">
       <c r="A4" s="3" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="C4" s="4"/>
       <c r="D4" s="4"/>
@@ -2877,10 +2881,10 @@
     </row>
     <row customHeight="1" ht="13.5" r="5" spans="1:5">
       <c r="A5" s="3" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="C5" s="4"/>
       <c r="D5" s="4"/>
